--- a/output/pdf_financials_xlsx/AIML.xlsx
+++ b/output/pdf_financials_xlsx/AIML.xlsx
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.697185</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.517045</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>10.289415</v>
       </c>
     </row>
     <row r="93">
@@ -3288,7 +3288,11 @@
           <t>Reserves 16,17</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -3930,7 +3934,11 @@
           <t>Reserves (Notes 12, 13 and 14)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>5.697185</v>
       </c>

--- a/output/pdf_financials_xlsx/AIML.xlsx
+++ b/output/pdf_financials_xlsx/AIML.xlsx
@@ -583,7 +583,7 @@
         <v>2.001804</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.685178</v>
+        <v>5.109153</v>
       </c>
     </row>
     <row r="11">
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00052</v>
       </c>
     </row>
     <row r="13">
@@ -873,7 +873,7 @@
         <v>-3.290428</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.590896</v>
+        <v>-4.591416</v>
       </c>
     </row>
     <row r="28">
@@ -905,7 +905,7 @@
         <v>-3.248376</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.564996</v>
+        <v>-4.565516</v>
       </c>
     </row>
     <row r="30">
@@ -921,7 +921,7 @@
         <v>-541.2724094665052</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-2728.514646727274</v>
+        <v>-2728.825452611069</v>
       </c>
     </row>
     <row r="31">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.00453</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.201452</v>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.010033</v>
+        <v>0.014563</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.21686</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.116491</v>
+        <v>0.111961</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.037892</v>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="F150" s="5" t="n">
-        <v>-2.001804</v>
+        <v>2.001804</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>-5.109153</v>
+        <v>5.109153</v>
       </c>
     </row>
     <row r="151">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">

--- a/output/pdf_financials_xlsx/AIML.xlsx
+++ b/output/pdf_financials_xlsx/AIML.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.280887</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.158454</v>
+        <v>0.408775</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.39849</v>
+        <v>1.9825</v>
       </c>
     </row>
     <row r="8">
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="68">
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.050612</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.030291</v>
       </c>
     </row>
     <row r="71">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0.01222</v>
+        <v>0.062832</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0.01222</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.030291</v>
       </c>
     </row>
     <row r="72">
@@ -1638,7 +1638,7 @@
         <v>0.986228</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.304938</v>
+        <v>0.274647</v>
       </c>
     </row>
     <row r="76">
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>-0.03902719448126088</v>
+        <v>-0.2006674863867908</v>
       </c>
       <c r="C80" s="3" t="n">
         <v>-0.009788858644715698</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.01445163817344741</v>
+        <v>0.02646037742431553</v>
       </c>
     </row>
     <row r="81">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001151</v>
       </c>
     </row>
     <row r="112">
@@ -2583,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001151</v>
       </c>
     </row>
     <row r="135">
@@ -2599,7 +2599,7 @@
         <v>-1.640504</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-3.993223</v>
+        <v>-3.994374</v>
       </c>
     </row>
   </sheetData>
@@ -3123,7 +3123,11 @@
           <t>Lease liabilities 8</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3837,7 +3841,11 @@
           <t>Lease liabilities (Note 9)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>0.050612</v>
       </c>
@@ -4814,7 +4822,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -6190,7 +6202,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E113" s="5" t="n">
         <v>0.292065</v>
       </c>
@@ -7043,7 +7059,11 @@
           <t>Management and director fees 15</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -8882,7 +8902,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E199" s="5" t="n">
         <v>0.160887</v>
       </c>
@@ -8911,7 +8935,11 @@
           <t>Management and director fees (Note 11)</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E200" s="5" t="n">
         <v>0.12</v>
       </c>
